--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.5604946861849</v>
+        <v>9.516080386505047</v>
       </c>
       <c r="D2" t="n">
-        <v>62.51270303783544</v>
+        <v>10.15831424364826</v>
       </c>
       <c r="E2" t="n">
-        <v>21.01516421489394</v>
+        <v>3.414964184920266</v>
       </c>
       <c r="F2" t="n">
-        <v>17.70954718918288</v>
+        <v>2.877801418242217</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.87802713116791</v>
+        <v>6.642679408814786</v>
       </c>
       <c r="D3" t="n">
-        <v>54.58685329441246</v>
+        <v>8.870363660342026</v>
       </c>
       <c r="E3" t="n">
-        <v>21.01516421489394</v>
+        <v>3.414964184920266</v>
       </c>
       <c r="F3" t="n">
-        <v>17.70954718918288</v>
+        <v>2.877801418242217</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.71769058885371</v>
+        <v>6.454124720688728</v>
       </c>
       <c r="D4" t="n">
-        <v>41.85186544131039</v>
+        <v>6.800928134212938</v>
       </c>
       <c r="E4" t="n">
-        <v>21.01516421489394</v>
+        <v>3.414964184920266</v>
       </c>
       <c r="F4" t="n">
-        <v>17.70954718918288</v>
+        <v>2.877801418242217</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>75.02906104948222</v>
+        <v>12.19222242054086</v>
       </c>
       <c r="D5" t="n">
-        <v>75.46688227966651</v>
+        <v>12.26336837044581</v>
       </c>
       <c r="E5" t="n">
-        <v>21.01516421489394</v>
+        <v>3.414964184920266</v>
       </c>
       <c r="F5" t="n">
-        <v>17.70954718918288</v>
+        <v>2.877801418242217</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.80285927349182</v>
+        <v>1.75546463194242</v>
       </c>
       <c r="D6" t="n">
-        <v>26.69959750080451</v>
+        <v>4.338684593880734</v>
       </c>
       <c r="E6" t="n">
-        <v>21.01516421489394</v>
+        <v>3.414964184920266</v>
       </c>
       <c r="F6" t="n">
-        <v>17.70954718918288</v>
+        <v>2.877801418242217</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.27502685709079</v>
+        <v>1.832191864277253</v>
       </c>
       <c r="D7" t="n">
-        <v>17.01383594205197</v>
+        <v>2.764748340583445</v>
       </c>
       <c r="E7" t="n">
-        <v>21.01516421489394</v>
+        <v>3.414964184920266</v>
       </c>
       <c r="F7" t="n">
-        <v>17.70954718918288</v>
+        <v>2.877801418242217</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.56330222357856</v>
+        <v>10.65403661133152</v>
       </c>
       <c r="D8" t="n">
-        <v>66.40145345311073</v>
+        <v>10.79023618613049</v>
       </c>
       <c r="E8" t="n">
-        <v>21.01516421489394</v>
+        <v>3.414964184920266</v>
       </c>
       <c r="F8" t="n">
-        <v>17.70954718918288</v>
+        <v>2.877801418242217</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>54.37821856948656</v>
+        <v>8.836460517541566</v>
       </c>
       <c r="D9" t="n">
-        <v>55.48189104988865</v>
+        <v>9.015807295606907</v>
       </c>
       <c r="E9" t="n">
-        <v>21.01516421489394</v>
+        <v>3.414964184920266</v>
       </c>
       <c r="F9" t="n">
-        <v>17.70954718918288</v>
+        <v>2.877801418242217</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>50.1771317311297</v>
+        <v>8.153783906308576</v>
       </c>
       <c r="D10" t="n">
-        <v>50.20549945176803</v>
+        <v>8.158393660912306</v>
       </c>
       <c r="E10" t="n">
-        <v>21.01516421489394</v>
+        <v>3.414964184920266</v>
       </c>
       <c r="F10" t="n">
-        <v>17.70954718918288</v>
+        <v>2.877801418242217</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
